--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3_task038.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3_task038.xlsx
@@ -100,13 +100,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
     <col min="2" max="2" width="14.85546875" customWidth="true"/>
     <col min="3" max="3" width="13.28515625" customWidth="true"/>
-    <col min="4" max="4" width="10" customWidth="true"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="9.5703125" customWidth="true"/>
     <col min="6" max="6" width="16.140625" customWidth="true"/>
     <col min="7" max="7" width="20.85546875" customWidth="true"/>
@@ -207,6 +207,94 @@
         <v>5.2591452473836515</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>312</v>
+      </c>
+      <c r="B3" s="0">
+        <v>113</v>
+      </c>
+      <c r="C3" s="0">
+        <v>312</v>
+      </c>
+      <c r="D3" s="0">
+        <v>93.390011832929559</v>
+      </c>
+      <c r="E3" s="0">
+        <v>482.94499999999999</v>
+      </c>
+      <c r="F3" s="0">
+        <v>152.50513448433438</v>
+      </c>
+      <c r="G3" s="0">
+        <v>6583.0576983766759</v>
+      </c>
+      <c r="H3" s="0">
+        <v>-1535.8328899148373</v>
+      </c>
+      <c r="I3" s="0">
+        <v>5.9050000000000002</v>
+      </c>
+      <c r="J3" s="0">
+        <v>17.195</v>
+      </c>
+      <c r="K3" s="0">
+        <v>2.7750000000000004</v>
+      </c>
+      <c r="L3" s="0">
+        <v>3.8600000000000003</v>
+      </c>
+      <c r="M3" s="0">
+        <v>227.44934574357057</v>
+      </c>
+      <c r="N3" s="0">
+        <v>5.2591452473836515</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>312</v>
+      </c>
+      <c r="B4" s="0">
+        <v>114</v>
+      </c>
+      <c r="C4" s="0">
+        <v>312</v>
+      </c>
+      <c r="D4" s="0">
+        <v>93.336982248060806</v>
+      </c>
+      <c r="E4" s="0">
+        <v>486</v>
+      </c>
+      <c r="F4" s="0">
+        <v>151.54648595377955</v>
+      </c>
+      <c r="G4" s="0">
+        <v>6692.8404714580847</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-1478.6320150848635</v>
+      </c>
+      <c r="I4" s="0">
+        <v>6.0899999999999999</v>
+      </c>
+      <c r="J4" s="0">
+        <v>17.594999999999999</v>
+      </c>
+      <c r="K4" s="0">
+        <v>2.9550000000000001</v>
+      </c>
+      <c r="L4" s="0">
+        <v>4.0350000000000001</v>
+      </c>
+      <c r="M4" s="0">
+        <v>227.44741267948291</v>
+      </c>
+      <c r="N4" s="0">
+        <v>5.2591452473836515</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>